--- a/louvain_baseline_experiments/louvain_Baseline_arenas-jazz_normalized/louvain_Baseline_arenas-jazz_normalized_results.xlsx
+++ b/louvain_baseline_experiments/louvain_Baseline_arenas-jazz_normalized/louvain_Baseline_arenas-jazz_normalized_results.xlsx
@@ -550,13 +550,13 @@
         <v>0.4450268029905711</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006389199999830453</v>
+        <v>0.01028739999992467</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02958680000028835</v>
+        <v>0.05012560000022859</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1360206999997899</v>
+        <v>0.1805820999998105</v>
       </c>
     </row>
   </sheetData>
